--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_nuble.xlsx
@@ -81,12 +81,12 @@
     <t xml:space="preserve">Quirihue</t>
   </si>
   <si>
+    <t xml:space="preserve">Coihueco</t>
+  </si>
+  <si>
     <t xml:space="preserve">El Carmen</t>
   </si>
   <si>
-    <t xml:space="preserve">Coihueco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cobquecura</t>
   </si>
   <si>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:20</t>
+    <t xml:space="preserve">2026-09-09 23:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -793,7 +793,7 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>16104</v>
+        <v>16302</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2019</v>
@@ -810,7 +810,7 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>16302</v>
+        <v>16104</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2019</v>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:16</t>
+    <t xml:space="preserve">2026-09-17 14:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_nuble.xlsx
@@ -81,12 +81,12 @@
     <t xml:space="preserve">Quirihue</t>
   </si>
   <si>
+    <t xml:space="preserve">El Carmen</t>
+  </si>
+  <si>
     <t xml:space="preserve">Coihueco</t>
   </si>
   <si>
-    <t xml:space="preserve">El Carmen</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cobquecura</t>
   </si>
   <si>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:11</t>
+    <t xml:space="preserve">2026-09-23 12:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -793,7 +793,7 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>16302</v>
+        <v>16104</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2019</v>
@@ -810,7 +810,7 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>16104</v>
+        <v>16302</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2019</v>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:40</t>
+    <t xml:space="preserve">2026-10-02 14:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_nuble.xlsx
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Chillán</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Coelemu</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:15</t>
+    <t xml:space="preserve">2026-10-04 09:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:09</t>
+    <t xml:space="preserve">2026-10-05 11:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
